--- a/seo-geo/tracking/issue-tracker.xlsx
+++ b/seo-geo/tracking/issue-tracker.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Homepage</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>site-wide</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Links target: /listing-division-2/, /case-studies-2/, /logistics-division-2/, /marketing-division/.</t>
+          <t>Links target: /listing-division-2/, /logistics-division-2/, /case-studies-2/, /marketing-division/.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
